--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报销单与审核意见" sheetId="3" r:id="rId1"/>
     <sheet name="成本一览表" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
     <t>日期：</t>
   </si>
   <si>
-    <t>{expDate}</t>
+    <t>{expDateStr}</t>
   </si>
   <si>
     <t>流水号：</t>
@@ -114,7 +115,7 @@
     <t>其他</t>
   </si>
   <si>
-    <t>{item.optDate}</t>
+    <t>{item.optDateStr}</t>
   </si>
   <si>
     <t>{item.pointFrom}</t>
@@ -253,7 +254,7 @@
     <t>{cost.expItem}</t>
   </si>
   <si>
-    <t>{cost.desc}</t>
+    <t>{cost.descMemo}</t>
   </si>
   <si>
     <t>{cost.applyAmount}</t>
@@ -1078,7 +1079,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1103,6 +1104,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1148,6 +1152,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1193,7 +1200,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1909,338 +1916,338 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" spans="1:12">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="1:12">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:12">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
     </row>
-    <row r="4" s="16" customFormat="1" ht="60" customHeight="1" spans="1:12">
-      <c r="A4" s="19" t="s">
+    <row r="4" s="17" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="19" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19" t="s">
+      <c r="F4" s="22"/>
+      <c r="G4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="19" t="s">
+      <c r="I4" s="22"/>
+      <c r="J4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:12">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="25" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="25" t="s">
+      <c r="D5" s="28"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="25" t="s">
+      <c r="G5" s="29"/>
+      <c r="H5" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="25" t="s">
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="29"/>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:12">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="33" t="s">
+      <c r="D6" s="33"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="33" t="s">
+      <c r="G6" s="36"/>
+      <c r="H6" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="47"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="35" t="s">
+      <c r="I6" s="49"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="35"/>
+      <c r="L6" s="37"/>
     </row>
-    <row r="7" s="17" customFormat="1" ht="60" customHeight="1" spans="1:12">
-      <c r="A7" s="35" t="s">
+    <row r="7" s="18" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A7" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="36" t="s">
+      <c r="F7" s="39"/>
+      <c r="G7" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="36" t="s">
+      <c r="H7" s="39"/>
+      <c r="I7" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="K7" s="35" t="s">
+      <c r="J7" s="39"/>
+      <c r="K7" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="37"/>
     </row>
     <row r="8" ht="99.95" customHeight="1" spans="1:12">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="30" t="s">
+      <c r="F8" s="34"/>
+      <c r="G8" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="30" t="s">
+      <c r="H8" s="34"/>
+      <c r="I8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="30" t="s">
+      <c r="J8" s="34"/>
+      <c r="K8" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="34"/>
     </row>
     <row r="9" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="36" t="s">
+      <c r="I9" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="37"/>
-      <c r="K9" s="39" t="s">
+      <c r="J9" s="39"/>
+      <c r="K9" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="L9" s="39"/>
+      <c r="L9" s="41"/>
     </row>
     <row r="10" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="30" t="s">
+      <c r="H10" s="39"/>
+      <c r="I10" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="34"/>
     </row>
     <row r="11" ht="75" customHeight="1" spans="1:12">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
     </row>
     <row r="12" ht="75" customHeight="1" spans="1:12">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
     </row>
     <row r="13" ht="90" customHeight="1" spans="1:12">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
     </row>
     <row r="14" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44" t="s">
+      <c r="B14" s="46"/>
+      <c r="C14" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44" t="s">
+      <c r="D14" s="46"/>
+      <c r="E14" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="44"/>
-      <c r="G14" s="45" t="s">
+      <c r="F14" s="46"/>
+      <c r="G14" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
     </row>
     <row r="15" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44" t="s">
+      <c r="D15" s="46"/>
+      <c r="E15" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44" t="s">
+      <c r="F15" s="46"/>
+      <c r="G15" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -2281,7 +2288,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="28" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="30" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2342,125 +2349,125 @@
       <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="15"/>
+      <c r="K2" s="16"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" ht="409.5" customHeight="1" spans="1:11">
-      <c r="A4" s="9" t="s">
+    <row r="4" ht="175" customHeight="1" spans="1:11">
+      <c r="A4" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11" t="s">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11" t="s">
+      <c r="H4" s="12"/>
+      <c r="I4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" ht="20.25" spans="1:11">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2480,7 +2487,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="33" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="32" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="报销单与审核意见" sheetId="3" r:id="rId1"/>
     <sheet name="成本一览表" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16,报销单与审核意见!$W$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报销单与审核意见" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
   <si>
     <t xml:space="preserve">  {company}差旅费用报销单</t>
   </si>
@@ -285,6 +285,12 @@
   </si>
   <si>
     <t>{costTaxAmountTotal}</t>
+  </si>
+  <si>
+    <t>公司名称</t>
+  </si>
+  <si>
+    <t>{company}</t>
   </si>
 </sst>
 </file>
@@ -298,10 +304,10 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="179" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,13 +332,6 @@
     </font>
     <font>
       <sz val="25"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -949,137 +948,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1122,91 +1121,88 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1215,19 +1211,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1916,338 +1912,338 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" spans="1:12">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="1:12">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:12">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
     </row>
-    <row r="4" s="17" customFormat="1" ht="60" customHeight="1" spans="1:12">
-      <c r="A4" s="20" t="s">
+    <row r="4" s="16" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="20" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="20" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="20" t="s">
+      <c r="I4" s="21"/>
+      <c r="J4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="48"/>
+      <c r="L4" s="47"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:12">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="27" t="s">
+      <c r="D5" s="27"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="27" t="s">
+      <c r="G5" s="28"/>
+      <c r="H5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="28"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="27" t="s">
+      <c r="I5" s="27"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="29"/>
+      <c r="L5" s="28"/>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:12">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="35" t="s">
+      <c r="G6" s="35"/>
+      <c r="H6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="49"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="37" t="s">
+      <c r="I6" s="48"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="37"/>
+      <c r="L6" s="36"/>
     </row>
-    <row r="7" s="18" customFormat="1" ht="60" customHeight="1" spans="1:12">
-      <c r="A7" s="37" t="s">
+    <row r="7" s="17" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A7" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="39"/>
-      <c r="G7" s="38" t="s">
+      <c r="F7" s="38"/>
+      <c r="G7" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="38" t="s">
+      <c r="H7" s="38"/>
+      <c r="I7" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="37" t="s">
+      <c r="J7" s="38"/>
+      <c r="K7" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="37"/>
+      <c r="L7" s="36"/>
     </row>
     <row r="8" ht="99.95" customHeight="1" spans="1:12">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="32" t="s">
+      <c r="F8" s="33"/>
+      <c r="G8" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="32" t="s">
+      <c r="H8" s="33"/>
+      <c r="I8" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="34"/>
-      <c r="K8" s="32" t="s">
+      <c r="J8" s="33"/>
+      <c r="K8" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="41" t="s">
+      <c r="J9" s="38"/>
+      <c r="K9" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="L9" s="41"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="39"/>
-      <c r="I10" s="32" t="s">
+      <c r="H10" s="38"/>
+      <c r="I10" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="34"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" ht="75" customHeight="1" spans="1:12">
-      <c r="A11" s="43"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
     </row>
     <row r="12" ht="75" customHeight="1" spans="1:12">
-      <c r="A12" s="44"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
     </row>
     <row r="13" ht="90" customHeight="1" spans="1:12">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
     </row>
     <row r="14" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46" t="s">
+      <c r="D14" s="45"/>
+      <c r="E14" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47" t="s">
+      <c r="F14" s="45"/>
+      <c r="G14" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
     </row>
     <row r="15" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46" t="s">
+      <c r="D15" s="45"/>
+      <c r="E15" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46" t="s">
+      <c r="F15" s="45"/>
+      <c r="G15" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -2355,10 +2351,10 @@
       <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="16"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
       <c r="A3" s="9" t="s">
@@ -2456,21 +2452,25 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
     </row>
-    <row r="7" ht="20.25" spans="1:11">
-      <c r="A7" s="14"/>
+    <row r="7" ht="77" customHeight="1" spans="1:11">
+      <c r="A7" s="14" t="s">
+        <v>84</v>
+      </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
+      <c r="D7" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="J2:K2"/>
@@ -2484,6 +2484,8 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="报销单与审核意见" sheetId="3" r:id="rId1"/>
     <sheet name="成本一览表" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16,报销单与审核意见!$W$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$11,报销单与审核意见!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
   <si>
     <t xml:space="preserve">  {company}差旅费用报销单</t>
   </si>
@@ -191,33 +191,6 @@
   </si>
   <si>
     <t>{verifyPayAmount}</t>
-  </si>
-  <si>
-    <t>审批意见</t>
-  </si>
-  <si>
-    <t>节点名称</t>
-  </si>
-  <si>
-    <t>操作人</t>
-  </si>
-  <si>
-    <t>操作类型</t>
-  </si>
-  <si>
-    <t>意见</t>
-  </si>
-  <si>
-    <t>{commentList.taskName}</t>
-  </si>
-  <si>
-    <t>{commentList.userName}</t>
-  </si>
-  <si>
-    <t>{commentList.operateText}</t>
-  </si>
-  <si>
-    <t>{commentList.comment}</t>
   </si>
   <si>
     <t xml:space="preserve">成本一览表
@@ -307,7 +280,7 @@
     <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,14 +326,6 @@
     <font>
       <b/>
       <sz val="48"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -948,137 +913,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1205,22 +1170,7 @@
     <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1503,57 +1453,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>71437</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="直接连接符 3"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9638030"/>
-          <a:ext cx="26169620" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:prstDash val="dash"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:prstClr val="black"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1894,7 +1793,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30.625" customWidth="1"/>
@@ -1980,10 +1879,10 @@
       <c r="J4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="42"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:12">
       <c r="A5" s="24" t="s">
@@ -2026,7 +1925,7 @@
       <c r="H6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="48"/>
+      <c r="I6" s="43"/>
       <c r="J6" s="35"/>
       <c r="K6" s="36" t="s">
         <v>18</v>
@@ -2157,96 +2056,8 @@
       <c r="K10" s="32"/>
       <c r="L10" s="33"/>
     </row>
-    <row r="11" ht="75" customHeight="1" spans="1:12">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-    </row>
-    <row r="12" ht="75" customHeight="1" spans="1:12">
-      <c r="A12" s="43"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-    </row>
-    <row r="13" ht="90" customHeight="1" spans="1:12">
-      <c r="A13" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-    </row>
-    <row r="14" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A14" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-    </row>
-    <row r="15" ht="80.1" customHeight="1" spans="1:12">
-      <c r="A15" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="24">
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
@@ -2270,17 +2081,7 @@
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="I10:L10"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:L15"/>
     <mergeCell ref="A1:L3"/>
-    <mergeCell ref="A11:L12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
@@ -2314,7 +2115,7 @@
   <sheetData>
     <row r="1" ht="132" customHeight="1" spans="1:11">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2358,108 +2159,108 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="175" customHeight="1" spans="1:11">
       <c r="A4" s="10" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="80.1" customHeight="1" spans="1:11">
       <c r="A5" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
     </row>
     <row r="6" ht="80.1" customHeight="1" spans="1:11">
       <c r="A6" s="13" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
     </row>
     <row r="7" ht="77" customHeight="1" spans="1:11">
       <c r="A7" s="14" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="成本一览表" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$11,报销单与审核意见!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16,报销单与审核意见!$W$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
   <si>
     <t xml:space="preserve">  {company}差旅费用报销单</t>
   </si>
@@ -191,6 +191,27 @@
   </si>
   <si>
     <t>{verifyPayAmount}</t>
+  </si>
+  <si>
+    <t>审批意见</t>
+  </si>
+  <si>
+    <t>节点名称</t>
+  </si>
+  <si>
+    <t>操作人</t>
+  </si>
+  <si>
+    <t>操作类型</t>
+  </si>
+  <si>
+    <t>{commentList.taskName}</t>
+  </si>
+  <si>
+    <t>{commentList.userName}</t>
+  </si>
+  <si>
+    <t>{commentList.operateText}</t>
   </si>
   <si>
     <t xml:space="preserve">成本一览表
@@ -280,7 +301,7 @@
     <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +347,14 @@
     <font>
       <b/>
       <sz val="48"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -913,137 +942,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1170,7 +1199,34 @@
     <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1453,6 +1509,57 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直接连接符 3"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9638030"/>
+          <a:ext cx="26169620" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:prstClr val="black"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1793,7 +1900,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30.625" customWidth="1"/>
@@ -1879,10 +1986,10 @@
       <c r="J4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="42" t="s">
+      <c r="K4" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="42"/>
+      <c r="L4" s="51"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:12">
       <c r="A5" s="24" t="s">
@@ -1925,7 +2032,7 @@
       <c r="H6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="43"/>
+      <c r="I6" s="52"/>
       <c r="J6" s="35"/>
       <c r="K6" s="36" t="s">
         <v>18</v>
@@ -2056,8 +2163,92 @@
       <c r="K10" s="32"/>
       <c r="L10" s="33"/>
     </row>
+    <row r="11" ht="75" customHeight="1" spans="1:12">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+    </row>
+    <row r="12" ht="75" customHeight="1" spans="1:12">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+    </row>
+    <row r="13" ht="90" customHeight="1" spans="1:12">
+      <c r="A13" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+    </row>
+    <row r="14" ht="80.1" customHeight="1" spans="1:12">
+      <c r="A14" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="46"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="49"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="47"/>
+    </row>
+    <row r="15" ht="80.1" customHeight="1" spans="1:12">
+      <c r="A15" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="46"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="49"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="47"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="32">
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
@@ -2081,7 +2272,15 @@
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="I10:L10"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:L15"/>
     <mergeCell ref="A1:L3"/>
+    <mergeCell ref="A11:L12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
@@ -2115,7 +2314,7 @@
   <sheetData>
     <row r="1" ht="132" customHeight="1" spans="1:11">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2159,108 +2358,108 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="175" customHeight="1" spans="1:11">
       <c r="A4" s="10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" ht="80.1" customHeight="1" spans="1:11">
       <c r="A5" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
     </row>
     <row r="6" ht="80.1" customHeight="1" spans="1:11">
       <c r="A6" s="13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
     </row>
     <row r="7" ht="77" customHeight="1" spans="1:11">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="成本一览表" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16,报销单与审核意见!$W$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="成本一览表" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审核意见!$A$1:$L$50</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Travel_Template.xlsx
@@ -61,13 +61,13 @@
     <t>{sn}</t>
   </si>
   <si>
-    <t>借支余额</t>
-  </si>
-  <si>
-    <t>本次冲借支</t>
-  </si>
-  <si>
-    <t>借支单编码</t>
+    <t>冲账类型</t>
+  </si>
+  <si>
+    <t>本次冲账金额</t>
+  </si>
+  <si>
+    <t>冲账单据编码</t>
   </si>
   <si>
     <t>项目合同编号</t>
@@ -76,7 +76,7 @@
     <t>研发编号</t>
   </si>
   <si>
-    <t>{cashBalance}</t>
+    <t>{offsetType}</t>
   </si>
   <si>
     <t>{offsetAmount}</t>
@@ -175,13 +175,13 @@
     <t>{verifyAmountTotal}</t>
   </si>
   <si>
-    <t>核定冲借支的金额</t>
+    <t>核定冲账金额</t>
   </si>
   <si>
     <t>{verifyOffsetAmount}</t>
   </si>
   <si>
-    <t>核定借支单编码</t>
+    <t>核定编码</t>
   </si>
   <si>
     <t>{verifyCashSn}</t>
